--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -427,13 +427,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C2" t="str">
-        <v>Admissions Open Now</v>
+        <v>Teachers Enrollment is OPEN</v>
       </c>
       <c r="D2" t="str">
-        <v>Enroll your child in Sankalp Marathi Shala for the upcoming academic year (September – June). Open to children aged 4 and above.</v>
+        <v>Teacher enrollment is officially open for the upcoming term! Secure your spot today to access new resources, professional development, and community support.</v>
       </c>
       <c r="E2" t="str">
         <v>Email Us to Enroll</v>

--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -439,7 +439,7 @@
         <v>Email Us to Enroll</v>
       </c>
       <c r="F2" t="str">
-        <v>mailto:sankalpmarathimandal@gmail.com?subject=Marathi%20Shala%20Admission</v>
+        <v>mailto:sankalpmarathishala@gmail.com?subject=Marathi%20Shala%20Admission</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>

--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -430,7 +430,7 @@
         <v>Yes</v>
       </c>
       <c r="C2" t="str">
-        <v>Teachers Enrollment is OPEN</v>
+        <v>Teachers Volunteer Enrollment is OPEN</v>
       </c>
       <c r="D2" t="str">
         <v>Teacher enrollment is officially open for the upcoming term! Secure your spot today to access new resources, professional development, and community support.</v>
@@ -439,7 +439,7 @@
         <v>Email Us to Enroll</v>
       </c>
       <c r="F2" t="str">
-        <v>mailto:sankalpmarathishala@gmail.com?subject=Marathi%20Shala%20Admission</v>
+        <v>https://docs.google.com/forms/d/e/1FAIpQLSft2wHeccFigGzz56Arbg8LJ6JHMaUzMac4atr6cUkoqGnqjg/viewform</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>

--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -430,7 +430,7 @@
         <v>Yes</v>
       </c>
       <c r="C2" t="str">
-        <v>Teachers Volunteer Enrollment is OPEN</v>
+        <v>Teachers Enrollment is OPEN</v>
       </c>
       <c r="D2" t="str">
         <v>Teacher enrollment is officially open for the upcoming term! Secure your spot today to access new resources, professional development, and community support.</v>

--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -430,13 +430,13 @@
         <v>Yes</v>
       </c>
       <c r="C2" t="str">
-        <v>Teachers Enrollment is OPEN</v>
+        <v>Teachers Volunteer Enrollment is OPEN</v>
       </c>
       <c r="D2" t="str">
         <v>Teacher enrollment is officially open for the upcoming term! Secure your spot today to access new resources, professional development, and community support.</v>
       </c>
       <c r="E2" t="str">
-        <v>Email Us to Enroll</v>
+        <v>Form to enroll</v>
       </c>
       <c r="F2" t="str">
         <v>https://docs.google.com/forms/d/e/1FAIpQLSft2wHeccFigGzz56Arbg8LJ6JHMaUzMac4atr6cUkoqGnqjg/viewform</v>

--- a/data/shala-admissions.xlsx
+++ b/data/shala-admissions.xlsx
@@ -436,7 +436,7 @@
         <v>Teacher enrollment is officially open for the upcoming term! Secure your spot today to access new resources, professional development, and community support.</v>
       </c>
       <c r="E2" t="str">
-        <v>Form to enroll</v>
+        <v>Form to enroll to create new sharp minds</v>
       </c>
       <c r="F2" t="str">
         <v>https://docs.google.com/forms/d/e/1FAIpQLSft2wHeccFigGzz56Arbg8LJ6JHMaUzMac4atr6cUkoqGnqjg/viewform</v>
